--- a/OBGYN_Job_Tracker.xlsx
+++ b/OBGYN_Job_Tracker.xlsx
@@ -414,21 +414,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -3542,6 +3542,3356 @@
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Staff Specialist- Obstetrics and Gynaecology</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT Government</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:29</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://jobs.nt.gov.au/Home/JobDetails?rtfId=352083</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>District Medical Officer Procedural and Non-Procedural Pool - East Kimberley</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Emergency Medicine</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Medical Officer</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>WA Health</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/district-medical-officer-procedural-and-non-procedural-pool-east-kimberley-kununurra-health-campus-wa-australia-wa-country-health-service</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Consultant - Obstetrics and Gynaecology</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>WA Health</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/consultant-obstetrics-and-gynaecology-armadale-health-service-wa-australia</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Registrar - Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Goulburn Valley Health</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:31</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://careers.gvhealth.org.au/job/Shepparton-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3630/1363898366/</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>GV_Health</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Specialist - Obstetrician &amp; Gynaecologist</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Goulburn Valley Health</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:31</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://careers.gvhealth.org.au/job/Shepparton-Specialist-Obstetrician-&amp;-Gynaecologist-VIC-3630/1363716466/</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>GV_Health</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Obstetrician &amp; Gynaecologist VMO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Albury Wodonga Health</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:31</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://careers.awh.org.au/job/Wodonga-Obstetrician-&amp;-Gynaecologist-VMO/1363723866/</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>AWH</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Emergency Medicine and Obstetrics and Gynaecology Senior Resident Medical Officer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Resident Doctor</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ACT Health / Canberra Health Services</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://acthealth.taleo.net/careersection/external/jobdetail.ftl?job=02QLE&amp;tz=GMT%2B05%3A30&amp;tzname=Asia%2FCalcutta</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ACT_Health</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Accredited Registrar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ACT Health / Canberra Health Services</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://acthealth.taleo.net/careersection/external/jobdetail.ftl?job=02QM1&amp;tz=GMT%2B05%3A30&amp;tzname=Asia%2FCalcutta</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ACT_Health</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Unaccredited Registrar</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ACT Health / Canberra Health Services</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://acthealth.taleo.net/careersection/external/jobdetail.ftl?job=02QM2&amp;tz=GMT%2B05%3A30&amp;tzname=Asia%2FCalcutta</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ACT_Health</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Senior Resident Medical Officer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Resident Doctor</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ACT Health / Canberra Health Services</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://acthealth.taleo.net/careersection/external/jobdetail.ftl?job=02QM3&amp;tz=GMT%2B05%3A30&amp;tzname=Asia%2FCalcutta</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ACT_Health</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>O&amp;G - Registrar - Kalgoorlie Health Campus</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://wave.com.au/job-listing/O%26G%20-%20Registrar%20-%20Kalgoorlie%20Health%20Campus%20-%20123357?hsLang=en-au</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>WAVE</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Staff Specialist or Staff Specialist (Obstetrics &amp; Gynaecology) CAIRNS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Department of Health</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cairns and Hinterland Hospital and Health Service, Esplanade, Cairns North QLD, Australia</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://jobs.ranzcog.edu.au/job/1599/senior-staff-specialist-or-staff-specialist-obstetrics-gynaecology-cairns/</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital RANZCOG Advanced training registrars 2027</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Senior Registrar</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital, Rocklands Drive, Tiwi NT, Australia</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://jobs.ranzcog.edu.au/job/1556/royal-darwin-hospital-ranzcog-advanced-training-registrars-2027/</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital Prevocational or Associate Trainee Registrar Positions 2027</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Royal Darwin Hospital, Rocklands Drive, Tiwi NT, Australia</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:32</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://jobs.ranzcog.edu.au/job/1557/royal-darwin-hospital-prevocational-or-associate-trainee-registrar-positions-2027/</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2027 O&amp;G Hospital Medical Officer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Medical Officer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The Royal Women's Hospital</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:35</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://careers.thewomens.org.au/job/2027-O&amp;amp;G-Hospital-Medical-Officer/2145-en_GB</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>The_Womens_OG</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Registered Midwife - Obstetrics and Maternity</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Monash Health</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:35</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://careers.monashhealth.org/job/Dandenong-Registered-Midwife-Obstetrics-and-Maternity-VIC-3175/1364948166/</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Monash_Health_OG</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Clinical Director of Obstetrics</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Eastern Health</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:35</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-Clinical-Director-of-Obstetrics-VIC-3128/1363712566/</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Eastern_Health_OG</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Renal Physician (Obstetric Medicine) - Internal Locum</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Eastern Health</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:35</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://careers.easternhealth.org.au/job/Box-Hill-Renal-Physician-%28Obstetric-Medicine%29-Internal-Locum-VIC-3128/1364154566/</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Eastern_Health_OG</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Skip to jobs search results</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Senior Registrar</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>WA Health</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>28-07-2026</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:35</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://medcareerswa.health.wa.gov.au#jobs_search_results_0f2490b2754df67a51a2aa8e3a11d384</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>WA_Health_OG</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology Registrar - 2027 Clinical Year</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Victorian Government</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:36</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://careers.vic.gov.au/job/obstetrics-gynaecology-registrar-2027-clinical-year-74149</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Careers_VIC_OG</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Specialist - Obstetrician &amp; Gynaecologist (Relocate to Regional VIC)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93567856</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Specialist - Obstetrician &amp; Gynaecologist (Relocate to Regional VIC)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93567467</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Principal House Officer/Registrar    Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93476242</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unaccredited Registrar (O&amp;G) 2027</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93080189</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93379834</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93026224</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology Registrar - 2027 Clinical Year</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93190793</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Registrar - Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93158598</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Medical Secretary OBGYN &amp; IVF - FULL TIME</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93355430</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2027 Statewide Obstetric Medicine Registrar / Advanced Trainee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93381980</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Clinical Director Support Officer (Obstetrics and Gynaecology)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93389437</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Specialist - Obstetrician &amp; Gynaecologist</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93222709</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Staff Specialist Obstetrician and Gynaecologist</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93527674</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Staff Specialist or Staff Specialist (Obstetrics &amp; Gynaecology) CAIRNS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93560793</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Obstetrician &amp; Gynaecologist VMO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93158093</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Consultant Obstetrics &amp; Gynaecology - WA Country Health Service</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93505746</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Principal House Officer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93043497</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Visiting Medical Officer - Obstetrician</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93384166</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Specialist Obstetricians &amp; Gynaecologists | Regional Australia</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93418567</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Visiting Medical Officer - Obstetrician</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93384362</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Consultant Obstetrician &amp; Gynaecologist</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93485878</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology- Staff Specialist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93542225</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VR General Practitioner | Women's Health Focus | Myhealth Darling Square</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://www.seek.com.au/job/93598836</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Seek</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Coffs Harbour Health Campus</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-e2ded435efee5490ebbddc5492c075d7</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Registrar Obstetrics and Gynaecology - Manning</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Registrar-Obstetrics-and-81c2bb814f9a8cb1a9fea900987aa58b</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Registrar Obstetrics and Gynaecology - General - Coffs Harbour</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Registrar-Obstetrics-and-aa08c08fe5988df34133b5c133daf93c</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Registrar Obstetrics and Gynaecology - General - Dubbo</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Registrar-Obstetrics-and-9c58146fd4e6e13e3e019c0bfbbc50c0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2027 Obstetrics &amp; Gynaecology Registrar (Non-Accredited) | EOI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/2027-Obstetrics-Gynaecology-519efd5556f7e9c257fabae8cf18431f</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology Registrar Need - Multiple Blocks</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetrics-Gynaecology-Registrar-4d13a5fa105c333103234d4f2d1796c8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Queanbeyan Hospital And Health Service</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-1b87adde3c615702ae5b427a8bbedcb5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>O&amp;G Registrar | Supportive Regional Hospital in NSW | Coastal Lifestyle</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/O-G-Registrar-72315e24ad1c83f1382280ef8090ef70</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Queanbeyan Hospital And Health Service</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-950afe3efebb90a9a40e861d2c5541eb</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology Registrar/medical-jobs/</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetrics-Gynaecology-Registrar-8c06916d2270c09b0db06da8a0ca8304</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Consultant - Maitland Hospital</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetrics-and-Gynaecology-839ec37d88139a3affde3f07c23ec657</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Consultant - Maitland Hospital</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetrics-and-Gynaecology-c7f320000ca91bb66feb947f23270291</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Consultant - Maitland Hospital</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetrics-and-Gynaecology-8b910de58c5594505fb557962ad13420</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Lismore Base Hospital</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-2b460779936f859c7bc55055505bcd31</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Manning Hospital</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-bd037deddb478d4896cdbb1c4f5353cf</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Manning Hospital</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-f2f8e4be1f1216acac59a589452ca080</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology - Registrar - Gosford</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Obstetric-and-Gynaecology-Registrar-147b2b611338b1044b2e88a785091220</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Consultant Obstetrician &amp; Gynaecologist | Regional SA</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Consultant-Obstetrician-Gynaecologist-d91f52550b8c607d8fe000ffd80ff5e1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Obstetrician &amp; Gynaecologist Specialist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>28-07-2026 18:37</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://au.jora.com/job/Specialist-61cae68a208f8f441da51e22b50b8cd0</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Jora</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynaecology Registrar / OBGYN</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3589,7 +6939,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28-07-2026 17:03</t>
+          <t>28-07-2026 18:37</t>
         </is>
       </c>
     </row>
@@ -3600,7 +6950,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
